--- a/data/fig7/suppFigData.xlsx
+++ b/data/fig7/suppFigData.xlsx
@@ -162,30 +162,30 @@
     <t xml:space="preserve">PLX+PTX+aPD-1_NR_PLX+PTX+aPD-L1</t>
   </si>
   <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">geoSample</t>
+  </si>
+  <si>
     <t xml:space="preserve">Treatment</t>
   </si>
   <si>
-    <t xml:space="preserve">geoSample</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
     <t xml:space="preserve">Clonality</t>
   </si>
   <si>
     <t xml:space="preserve">yPos</t>
   </si>
   <si>
+    <t xml:space="preserve">d80 WTNT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APL3</t>
+  </si>
+  <si>
     <t xml:space="preserve">WTNT</t>
   </si>
   <si>
-    <t xml:space="preserve">APL3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d80 WTNT</t>
-  </si>
-  <si>
     <t xml:space="preserve">APL4</t>
   </si>
   <si>
@@ -195,24 +195,24 @@
     <t xml:space="preserve">APL6</t>
   </si>
   <si>
+    <t xml:space="preserve">d80 Untreated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APL1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Untreated</t>
   </si>
   <si>
-    <t xml:space="preserve">APL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d80 Untreated</t>
-  </si>
-  <si>
     <t xml:space="preserve">APL2</t>
   </si>
   <si>
+    <t xml:space="preserve">d105 WTNT</t>
+  </si>
+  <si>
     <t xml:space="preserve">APL103</t>
   </si>
   <si>
-    <t xml:space="preserve">d105 WTNT</t>
-  </si>
-  <si>
     <t xml:space="preserve">APL104</t>
   </si>
   <si>
@@ -225,12 +225,12 @@
     <t xml:space="preserve">APL107</t>
   </si>
   <si>
+    <t xml:space="preserve">d105 Untreated</t>
+  </si>
+  <si>
     <t xml:space="preserve">APL14</t>
   </si>
   <si>
-    <t xml:space="preserve">d105 Untreated</t>
-  </si>
-  <si>
     <t xml:space="preserve">APL15</t>
   </si>
   <si>
@@ -264,15 +264,15 @@
     <t xml:space="preserve">APL25</t>
   </si>
   <si>
+    <t xml:space="preserve">d105 PTX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APL33</t>
+  </si>
+  <si>
     <t xml:space="preserve">PTX</t>
   </si>
   <si>
-    <t xml:space="preserve">APL33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d105 PTX</t>
-  </si>
-  <si>
     <t xml:space="preserve">APL34</t>
   </si>
   <si>
@@ -309,15 +309,15 @@
     <t xml:space="preserve">APL102</t>
   </si>
   <si>
+    <t xml:space="preserve">d105 PLX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APL76</t>
+  </si>
+  <si>
     <t xml:space="preserve">PLX</t>
   </si>
   <si>
-    <t xml:space="preserve">APL76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d105 PLX</t>
-  </si>
-  <si>
     <t xml:space="preserve">APL77</t>
   </si>
   <si>
@@ -342,15 +342,15 @@
     <t xml:space="preserve">APL84</t>
   </si>
   <si>
+    <t xml:space="preserve">d105 PLX+PTX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APL40</t>
+  </si>
+  <si>
     <t xml:space="preserve">PLX+PTX</t>
   </si>
   <si>
-    <t xml:space="preserve">APL40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d105 PLX+PTX</t>
-  </si>
-  <si>
     <t xml:space="preserve">APL41</t>
   </si>
   <si>
@@ -399,15 +399,15 @@
     <t xml:space="preserve">APL100</t>
   </si>
   <si>
+    <t xml:space="preserve">d105 PTX+aPD-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APL64</t>
+  </si>
+  <si>
     <t xml:space="preserve">PTX+aPD-1</t>
   </si>
   <si>
-    <t xml:space="preserve">APL64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d105 PTX+aPD-1</t>
-  </si>
-  <si>
     <t xml:space="preserve">APL65</t>
   </si>
   <si>
@@ -429,12 +429,12 @@
     <t xml:space="preserve">APL71</t>
   </si>
   <si>
+    <t xml:space="preserve">d105 PLX+PTX+aPD-1_R</t>
+  </si>
+  <si>
     <t xml:space="preserve">APL51</t>
   </si>
   <si>
-    <t xml:space="preserve">d105 PLX+PTX+aPD-1_R</t>
-  </si>
-  <si>
     <t xml:space="preserve">APL52</t>
   </si>
   <si>
@@ -462,12 +462,12 @@
     <t xml:space="preserve">APL93</t>
   </si>
   <si>
+    <t xml:space="preserve">d105 PLX+PTX+aPD-1_NR</t>
+  </si>
+  <si>
     <t xml:space="preserve">APL54</t>
   </si>
   <si>
-    <t xml:space="preserve">d105 PLX+PTX+aPD-1_NR</t>
-  </si>
-  <si>
     <t xml:space="preserve">APL55</t>
   </si>
   <si>
@@ -489,15 +489,15 @@
     <t xml:space="preserve">APL95</t>
   </si>
   <si>
+    <t xml:space="preserve">d105 aPD-L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APL7</t>
+  </si>
+  <si>
     <t xml:space="preserve">aPD-L1</t>
   </si>
   <si>
-    <t xml:space="preserve">APL7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d105 aPD-L1</t>
-  </si>
-  <si>
     <t xml:space="preserve">APL8</t>
   </si>
   <si>
@@ -516,15 +516,15 @@
     <t xml:space="preserve">APL13</t>
   </si>
   <si>
+    <t xml:space="preserve">d105 PTX+aPD-L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APL26</t>
+  </si>
+  <si>
     <t xml:space="preserve">PTX+aPD-L1</t>
   </si>
   <si>
-    <t xml:space="preserve">APL26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d105 PTX+aPD-L1</t>
-  </si>
-  <si>
     <t xml:space="preserve">APL27</t>
   </si>
   <si>
@@ -543,10 +543,10 @@
     <t xml:space="preserve">APL32</t>
   </si>
   <si>
+    <t xml:space="preserve">d105 PLX+PTX+aPD-L1</t>
+  </si>
+  <si>
     <t xml:space="preserve">APL46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d105 PLX+PTX+aPD-L1</t>
   </si>
   <si>
     <t xml:space="preserve">APL47</t>
@@ -9832,7 +9832,7 @@
         <v>0.045033592989288</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -9852,7 +9852,7 @@
         <v>0.045033592989288</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -9872,7 +9872,7 @@
         <v>0.045033592989288</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -9892,7 +9892,7 @@
         <v>0.045033592989288</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -9912,7 +9912,7 @@
         <v>0.045033592989288</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -9932,18 +9932,18 @@
         <v>0.045033592989288</v>
       </c>
       <c r="F7" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D8" t="n">
         <v>0.0794410343543349</v>
@@ -9952,18 +9952,18 @@
         <v>0.045033592989288</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B9" t="s">
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D9" t="n">
         <v>0.0651978279992738</v>
@@ -9972,18 +9972,18 @@
         <v>0.045033592989288</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B10" t="s">
         <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D10" t="n">
         <v>0.0654021874716456</v>
@@ -9992,18 +9992,18 @@
         <v>0.045033592989288</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B11" t="s">
         <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D11" t="n">
         <v>0.0793136850942483</v>
@@ -10012,18 +10012,18 @@
         <v>0.045033592989288</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B12" t="s">
         <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
         <v>0.0979635032198232</v>
@@ -10032,18 +10032,18 @@
         <v>0.045033592989288</v>
       </c>
       <c r="F12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
         <v>0.0715750317376355</v>
@@ -10052,18 +10052,18 @@
         <v>0.045033592989288</v>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B14" t="s">
         <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D14" t="n">
         <v>0.115809738526573</v>
@@ -10072,18 +10072,18 @@
         <v>0.045033592989288</v>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B15" t="s">
         <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
         <v>0.1031747961191</v>
@@ -10092,18 +10092,18 @@
         <v>0.045033592989288</v>
       </c>
       <c r="F15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B16" t="s">
         <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
         <v>0.0899576541916195</v>
@@ -10112,18 +10112,18 @@
         <v>0.045033592989288</v>
       </c>
       <c r="F16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B17" t="s">
         <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D17" t="n">
         <v>0.10397396217838</v>
@@ -10132,18 +10132,18 @@
         <v>0.045033592989288</v>
       </c>
       <c r="F17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B18" t="s">
         <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D18" t="n">
         <v>0.115668121054304</v>
@@ -10152,18 +10152,18 @@
         <v>0.045033592989288</v>
       </c>
       <c r="F18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B19" t="s">
         <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D19" t="n">
         <v>0.0653790127568753</v>
@@ -10172,18 +10172,18 @@
         <v>0.045033592989288</v>
       </c>
       <c r="F19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B20" t="s">
         <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D20" t="n">
         <v>0.0917496132706112</v>
@@ -10192,18 +10192,18 @@
         <v>0.045033592989288</v>
       </c>
       <c r="F20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B21" t="s">
         <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D21" t="n">
         <v>0.0998579121433124</v>
@@ -10212,18 +10212,18 @@
         <v>0.045033592989288</v>
       </c>
       <c r="F21" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B22" t="s">
         <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D22" t="n">
         <v>0.107467089112536</v>
@@ -10232,18 +10232,18 @@
         <v>0.045033592989288</v>
       </c>
       <c r="F22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B23" t="s">
         <v>79</v>
       </c>
       <c r="C23" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D23" t="n">
         <v>0.0985517835732729</v>
@@ -10252,18 +10252,18 @@
         <v>0.045033592989288</v>
       </c>
       <c r="F23" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B24" t="s">
         <v>80</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D24" t="n">
         <v>0.112108419272873</v>
@@ -10272,7 +10272,7 @@
         <v>0.045033592989288</v>
       </c>
       <c r="F24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
@@ -11217,13 +11217,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="B72" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C72" t="s">
-        <v>137</v>
+        <v>10</v>
       </c>
       <c r="D72" t="n">
         <v>0.0569865259551919</v>
@@ -11237,13 +11237,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="B73" t="s">
         <v>138</v>
       </c>
       <c r="C73" t="s">
-        <v>137</v>
+        <v>10</v>
       </c>
       <c r="D73" t="n">
         <v>0.105780748825122</v>
@@ -11257,13 +11257,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="B74" t="s">
         <v>139</v>
       </c>
       <c r="C74" t="s">
-        <v>137</v>
+        <v>10</v>
       </c>
       <c r="D74" t="n">
         <v>0.0608870144460646</v>
@@ -11277,13 +11277,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="B75" t="s">
         <v>140</v>
       </c>
       <c r="C75" t="s">
-        <v>137</v>
+        <v>10</v>
       </c>
       <c r="D75" t="n">
         <v>0.0624485008104627</v>
@@ -11297,13 +11297,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="B76" t="s">
         <v>141</v>
       </c>
       <c r="C76" t="s">
-        <v>137</v>
+        <v>10</v>
       </c>
       <c r="D76" t="n">
         <v>0.0915700692179137</v>
@@ -11317,13 +11317,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="B77" t="s">
         <v>142</v>
       </c>
       <c r="C77" t="s">
-        <v>137</v>
+        <v>10</v>
       </c>
       <c r="D77" t="n">
         <v>0.121946960234437</v>
@@ -11337,13 +11337,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="B78" t="s">
         <v>143</v>
       </c>
       <c r="C78" t="s">
-        <v>137</v>
+        <v>10</v>
       </c>
       <c r="D78" t="n">
         <v>0.0778293422807759</v>
@@ -11357,13 +11357,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="B79" t="s">
         <v>144</v>
       </c>
       <c r="C79" t="s">
-        <v>137</v>
+        <v>10</v>
       </c>
       <c r="D79" t="n">
         <v>0.0965329546599247</v>
@@ -11377,13 +11377,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="B80" t="s">
         <v>145</v>
       </c>
       <c r="C80" t="s">
-        <v>137</v>
+        <v>10</v>
       </c>
       <c r="D80" t="n">
         <v>0.0641905686059629</v>
@@ -11397,13 +11397,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="B81" t="s">
         <v>146</v>
       </c>
       <c r="C81" t="s">
-        <v>137</v>
+        <v>10</v>
       </c>
       <c r="D81" t="n">
         <v>0.070331818828447</v>
@@ -11417,13 +11417,13 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="B82" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C82" t="s">
-        <v>148</v>
+        <v>11</v>
       </c>
       <c r="D82" t="n">
         <v>0.0615482771522575</v>
@@ -11437,13 +11437,13 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="B83" t="s">
         <v>149</v>
       </c>
       <c r="C83" t="s">
-        <v>148</v>
+        <v>11</v>
       </c>
       <c r="D83" t="n">
         <v>0.0586411936201892</v>
@@ -11457,13 +11457,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="B84" t="s">
         <v>150</v>
       </c>
       <c r="C84" t="s">
-        <v>148</v>
+        <v>11</v>
       </c>
       <c r="D84" t="n">
         <v>0.0593355982127924</v>
@@ -11477,13 +11477,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="B85" t="s">
         <v>151</v>
       </c>
       <c r="C85" t="s">
-        <v>148</v>
+        <v>11</v>
       </c>
       <c r="D85" t="n">
         <v>0.0528788943438723</v>
@@ -11497,13 +11497,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="B86" t="s">
         <v>152</v>
       </c>
       <c r="C86" t="s">
-        <v>148</v>
+        <v>11</v>
       </c>
       <c r="D86" t="n">
         <v>0.0854624858379408</v>
@@ -11517,13 +11517,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="B87" t="s">
         <v>153</v>
       </c>
       <c r="C87" t="s">
-        <v>148</v>
+        <v>11</v>
       </c>
       <c r="D87" t="n">
         <v>0.0938612598287016</v>
@@ -11537,13 +11537,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="B88" t="s">
         <v>154</v>
       </c>
       <c r="C88" t="s">
-        <v>148</v>
+        <v>11</v>
       </c>
       <c r="D88" t="n">
         <v>0.0690236606421187</v>
@@ -11557,13 +11557,13 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="B89" t="s">
         <v>155</v>
       </c>
       <c r="C89" t="s">
-        <v>148</v>
+        <v>11</v>
       </c>
       <c r="D89" t="n">
         <v>0.0945018300520376</v>
@@ -11857,13 +11857,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>29</v>
+        <v>174</v>
       </c>
       <c r="B104" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C104" t="s">
-        <v>175</v>
+        <v>29</v>
       </c>
       <c r="D104" t="n">
         <v>0.125926200666149</v>
@@ -11877,13 +11877,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>29</v>
+        <v>174</v>
       </c>
       <c r="B105" t="s">
         <v>176</v>
       </c>
       <c r="C105" t="s">
-        <v>175</v>
+        <v>29</v>
       </c>
       <c r="D105" t="n">
         <v>0.102345364079749</v>
@@ -11897,13 +11897,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>29</v>
+        <v>174</v>
       </c>
       <c r="B106" t="s">
         <v>177</v>
       </c>
       <c r="C106" t="s">
-        <v>175</v>
+        <v>29</v>
       </c>
       <c r="D106" t="n">
         <v>0.108833647635811</v>
@@ -11917,13 +11917,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>29</v>
+        <v>174</v>
       </c>
       <c r="B107" t="s">
         <v>178</v>
       </c>
       <c r="C107" t="s">
-        <v>175</v>
+        <v>29</v>
       </c>
       <c r="D107" t="n">
         <v>0.133769345599885</v>
@@ -11937,13 +11937,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>29</v>
+        <v>174</v>
       </c>
       <c r="B108" t="s">
         <v>179</v>
       </c>
       <c r="C108" t="s">
-        <v>175</v>
+        <v>29</v>
       </c>
       <c r="D108" t="n">
         <v>0.0869451349708371</v>
@@ -11971,10 +11971,10 @@
         <v>48</v>
       </c>
       <c r="B1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" t="s">
         <v>47</v>
-      </c>
-      <c r="C1" t="s">
-        <v>49</v>
       </c>
       <c r="D1" t="s">
         <v>180</v>
@@ -11997,10 +11997,10 @@
         <v>53</v>
       </c>
       <c r="B2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" t="s">
         <v>52</v>
-      </c>
-      <c r="C2" t="s">
-        <v>54</v>
       </c>
       <c r="D2" t="n">
         <v>0.0495452307532845</v>
@@ -12023,10 +12023,10 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" t="s">
         <v>52</v>
-      </c>
-      <c r="C3" t="s">
-        <v>54</v>
       </c>
       <c r="D3" t="n">
         <v>0.016487926500222</v>
@@ -12049,10 +12049,10 @@
         <v>56</v>
       </c>
       <c r="B4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" t="s">
         <v>52</v>
-      </c>
-      <c r="C4" t="s">
-        <v>54</v>
       </c>
       <c r="D4" t="n">
         <v>0.0345052979221137</v>
@@ -12075,10 +12075,10 @@
         <v>57</v>
       </c>
       <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" t="s">
         <v>52</v>
-      </c>
-      <c r="C5" t="s">
-        <v>54</v>
       </c>
       <c r="D5" t="n">
         <v>0.0236872862646639</v>
@@ -12101,10 +12101,10 @@
         <v>59</v>
       </c>
       <c r="B6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" t="s">
         <v>58</v>
-      </c>
-      <c r="C6" t="s">
-        <v>60</v>
       </c>
       <c r="D6" t="n">
         <v>0.0147072728366728</v>
@@ -12127,10 +12127,10 @@
         <v>61</v>
       </c>
       <c r="B7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" t="s">
         <v>58</v>
-      </c>
-      <c r="C7" t="s">
-        <v>60</v>
       </c>
       <c r="D7" t="n">
         <v>0.0343464230406534</v>
@@ -12150,13 +12150,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" t="s">
         <v>62</v>
-      </c>
-      <c r="B8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" t="s">
-        <v>63</v>
       </c>
       <c r="D8" t="n">
         <v>0.00636700231841932</v>
@@ -12179,10 +12179,10 @@
         <v>64</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D9" t="n">
         <v>0.0296446263191902</v>
@@ -12205,10 +12205,10 @@
         <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D10" t="n">
         <v>0.00899942943098708</v>
@@ -12231,10 +12231,10 @@
         <v>66</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D11" t="n">
         <v>0.0245202650746062</v>
@@ -12257,10 +12257,10 @@
         <v>67</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D12" t="n">
         <v>0.0564701213093821</v>
@@ -12280,13 +12280,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" t="s">
         <v>68</v>
-      </c>
-      <c r="B13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" t="s">
-        <v>69</v>
       </c>
       <c r="D13" t="n">
         <v>0.0135895154253527</v>
@@ -12309,10 +12309,10 @@
         <v>70</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
         <v>0.0371005106918022</v>
@@ -12335,10 +12335,10 @@
         <v>71</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
         <v>0.0170953507927839</v>
@@ -12361,10 +12361,10 @@
         <v>72</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
         <v>0.0275714335072384</v>
@@ -12387,10 +12387,10 @@
         <v>73</v>
       </c>
       <c r="B17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>0.0307032708664684</v>
@@ -12413,10 +12413,10 @@
         <v>74</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D18" t="n">
         <v>0.0452713258586016</v>
@@ -12439,10 +12439,10 @@
         <v>75</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D19" t="n">
         <v>0.0065103491207138</v>
@@ -12465,10 +12465,10 @@
         <v>76</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D20" t="n">
         <v>0.0248036128317818</v>
@@ -12491,10 +12491,10 @@
         <v>77</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D21" t="n">
         <v>0.0465154333746728</v>
@@ -12517,10 +12517,10 @@
         <v>78</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D22" t="n">
         <v>0.0243250467789361</v>
@@ -12543,10 +12543,10 @@
         <v>79</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D23" t="n">
         <v>0.0349917138516779</v>
@@ -12569,10 +12569,10 @@
         <v>80</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D24" t="n">
         <v>0.0304172691592646</v>
@@ -12595,10 +12595,10 @@
         <v>82</v>
       </c>
       <c r="B25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" t="s">
         <v>81</v>
-      </c>
-      <c r="C25" t="s">
-        <v>83</v>
       </c>
       <c r="D25" t="n">
         <v>0.0398825966850829</v>
@@ -12621,10 +12621,10 @@
         <v>84</v>
       </c>
       <c r="B26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" t="s">
         <v>81</v>
-      </c>
-      <c r="C26" t="s">
-        <v>83</v>
       </c>
       <c r="D26" t="n">
         <v>0.014273278113445</v>
@@ -12647,10 +12647,10 @@
         <v>85</v>
       </c>
       <c r="B27" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" t="s">
         <v>81</v>
-      </c>
-      <c r="C27" t="s">
-        <v>83</v>
       </c>
       <c r="D27" t="n">
         <v>0.00733099891328722</v>
@@ -12673,10 +12673,10 @@
         <v>86</v>
       </c>
       <c r="B28" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" t="s">
         <v>81</v>
-      </c>
-      <c r="C28" t="s">
-        <v>83</v>
       </c>
       <c r="D28" t="n">
         <v>0.0152090268470883</v>
@@ -12699,10 +12699,10 @@
         <v>87</v>
       </c>
       <c r="B29" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" t="s">
         <v>81</v>
-      </c>
-      <c r="C29" t="s">
-        <v>83</v>
       </c>
       <c r="D29" t="n">
         <v>0.0562950972119375</v>
@@ -12725,10 +12725,10 @@
         <v>88</v>
       </c>
       <c r="B30" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" t="s">
         <v>81</v>
-      </c>
-      <c r="C30" t="s">
-        <v>83</v>
       </c>
       <c r="D30" t="n">
         <v>0.128468715744409</v>
@@ -12751,10 +12751,10 @@
         <v>89</v>
       </c>
       <c r="B31" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" t="s">
         <v>81</v>
-      </c>
-      <c r="C31" t="s">
-        <v>83</v>
       </c>
       <c r="D31" t="n">
         <v>0.0186730370968712</v>
@@ -12777,10 +12777,10 @@
         <v>90</v>
       </c>
       <c r="B32" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" t="s">
         <v>81</v>
-      </c>
-      <c r="C32" t="s">
-        <v>83</v>
       </c>
       <c r="D32" t="n">
         <v>0.0125479442544994</v>
@@ -12803,10 +12803,10 @@
         <v>91</v>
       </c>
       <c r="B33" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" t="s">
         <v>81</v>
-      </c>
-      <c r="C33" t="s">
-        <v>83</v>
       </c>
       <c r="D33" t="n">
         <v>0.0950146123431322</v>
@@ -12829,10 +12829,10 @@
         <v>92</v>
       </c>
       <c r="B34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" t="s">
         <v>81</v>
-      </c>
-      <c r="C34" t="s">
-        <v>83</v>
       </c>
       <c r="D34" t="n">
         <v>0.0161217704509247</v>
@@ -12855,10 +12855,10 @@
         <v>93</v>
       </c>
       <c r="B35" t="s">
+        <v>83</v>
+      </c>
+      <c r="C35" t="s">
         <v>81</v>
-      </c>
-      <c r="C35" t="s">
-        <v>83</v>
       </c>
       <c r="D35" t="n">
         <v>0.00917565691321932</v>
@@ -12881,10 +12881,10 @@
         <v>94</v>
       </c>
       <c r="B36" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" t="s">
         <v>81</v>
-      </c>
-      <c r="C36" t="s">
-        <v>83</v>
       </c>
       <c r="D36" t="n">
         <v>0.0398050786683832</v>
@@ -12907,10 +12907,10 @@
         <v>95</v>
       </c>
       <c r="B37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" t="s">
         <v>81</v>
-      </c>
-      <c r="C37" t="s">
-        <v>83</v>
       </c>
       <c r="D37" t="n">
         <v>0.0155941878567722</v>
@@ -12933,10 +12933,10 @@
         <v>97</v>
       </c>
       <c r="B38" t="s">
+        <v>98</v>
+      </c>
+      <c r="C38" t="s">
         <v>96</v>
-      </c>
-      <c r="C38" t="s">
-        <v>98</v>
       </c>
       <c r="D38" t="n">
         <v>0.0300943461194133</v>
@@ -12959,10 +12959,10 @@
         <v>99</v>
       </c>
       <c r="B39" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" t="s">
         <v>96</v>
-      </c>
-      <c r="C39" t="s">
-        <v>98</v>
       </c>
       <c r="D39" t="n">
         <v>0.0322452846438722</v>
@@ -12985,10 +12985,10 @@
         <v>100</v>
       </c>
       <c r="B40" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" t="s">
         <v>96</v>
-      </c>
-      <c r="C40" t="s">
-        <v>98</v>
       </c>
       <c r="D40" t="n">
         <v>0.268565466335541</v>
@@ -13011,10 +13011,10 @@
         <v>101</v>
       </c>
       <c r="B41" t="s">
+        <v>98</v>
+      </c>
+      <c r="C41" t="s">
         <v>96</v>
-      </c>
-      <c r="C41" t="s">
-        <v>98</v>
       </c>
       <c r="D41" t="n">
         <v>0.0415887326857271</v>
@@ -13037,10 +13037,10 @@
         <v>102</v>
       </c>
       <c r="B42" t="s">
+        <v>98</v>
+      </c>
+      <c r="C42" t="s">
         <v>96</v>
-      </c>
-      <c r="C42" t="s">
-        <v>98</v>
       </c>
       <c r="D42" t="n">
         <v>0.0157626293261796</v>
@@ -13063,10 +13063,10 @@
         <v>103</v>
       </c>
       <c r="B43" t="s">
+        <v>98</v>
+      </c>
+      <c r="C43" t="s">
         <v>96</v>
-      </c>
-      <c r="C43" t="s">
-        <v>98</v>
       </c>
       <c r="D43" t="n">
         <v>0.0171457170223231</v>
@@ -13089,10 +13089,10 @@
         <v>104</v>
       </c>
       <c r="B44" t="s">
+        <v>98</v>
+      </c>
+      <c r="C44" t="s">
         <v>96</v>
-      </c>
-      <c r="C44" t="s">
-        <v>98</v>
       </c>
       <c r="D44" t="n">
         <v>0.0139794566507803</v>
@@ -13115,10 +13115,10 @@
         <v>105</v>
       </c>
       <c r="B45" t="s">
+        <v>98</v>
+      </c>
+      <c r="C45" t="s">
         <v>96</v>
-      </c>
-      <c r="C45" t="s">
-        <v>98</v>
       </c>
       <c r="D45" t="n">
         <v>0.0180082635321836</v>
@@ -13141,10 +13141,10 @@
         <v>106</v>
       </c>
       <c r="B46" t="s">
+        <v>98</v>
+      </c>
+      <c r="C46" t="s">
         <v>96</v>
-      </c>
-      <c r="C46" t="s">
-        <v>98</v>
       </c>
       <c r="D46" t="n">
         <v>0.0536520515543125</v>
@@ -13167,10 +13167,10 @@
         <v>108</v>
       </c>
       <c r="B47" t="s">
+        <v>109</v>
+      </c>
+      <c r="C47" t="s">
         <v>107</v>
-      </c>
-      <c r="C47" t="s">
-        <v>109</v>
       </c>
       <c r="D47" t="n">
         <v>0.0153518968159667</v>
@@ -13193,10 +13193,10 @@
         <v>110</v>
       </c>
       <c r="B48" t="s">
+        <v>109</v>
+      </c>
+      <c r="C48" t="s">
         <v>107</v>
-      </c>
-      <c r="C48" t="s">
-        <v>109</v>
       </c>
       <c r="D48" t="n">
         <v>0.0251978539626769</v>
@@ -13219,10 +13219,10 @@
         <v>111</v>
       </c>
       <c r="B49" t="s">
+        <v>109</v>
+      </c>
+      <c r="C49" t="s">
         <v>107</v>
-      </c>
-      <c r="C49" t="s">
-        <v>109</v>
       </c>
       <c r="D49" t="n">
         <v>0.0240177883908255</v>
@@ -13245,10 +13245,10 @@
         <v>112</v>
       </c>
       <c r="B50" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" t="s">
         <v>107</v>
-      </c>
-      <c r="C50" t="s">
-        <v>109</v>
       </c>
       <c r="D50" t="n">
         <v>0.0180197268588771</v>
@@ -13271,10 +13271,10 @@
         <v>113</v>
       </c>
       <c r="B51" t="s">
+        <v>109</v>
+      </c>
+      <c r="C51" t="s">
         <v>107</v>
-      </c>
-      <c r="C51" t="s">
-        <v>109</v>
       </c>
       <c r="D51" t="n">
         <v>0.00808709175738724</v>
@@ -13297,10 +13297,10 @@
         <v>114</v>
       </c>
       <c r="B52" t="s">
+        <v>109</v>
+      </c>
+      <c r="C52" t="s">
         <v>107</v>
-      </c>
-      <c r="C52" t="s">
-        <v>109</v>
       </c>
       <c r="D52" t="n">
         <v>0.0189951776144343</v>
@@ -13323,10 +13323,10 @@
         <v>115</v>
       </c>
       <c r="B53" t="s">
+        <v>109</v>
+      </c>
+      <c r="C53" t="s">
         <v>107</v>
-      </c>
-      <c r="C53" t="s">
-        <v>109</v>
       </c>
       <c r="D53" t="n">
         <v>0.0141049449362989</v>
@@ -13349,10 +13349,10 @@
         <v>116</v>
       </c>
       <c r="B54" t="s">
+        <v>109</v>
+      </c>
+      <c r="C54" t="s">
         <v>107</v>
-      </c>
-      <c r="C54" t="s">
-        <v>109</v>
       </c>
       <c r="D54" t="n">
         <v>0.0235716834004383</v>
@@ -13375,10 +13375,10 @@
         <v>117</v>
       </c>
       <c r="B55" t="s">
+        <v>109</v>
+      </c>
+      <c r="C55" t="s">
         <v>107</v>
-      </c>
-      <c r="C55" t="s">
-        <v>109</v>
       </c>
       <c r="D55" t="n">
         <v>0.00711220529654134</v>
@@ -13401,10 +13401,10 @@
         <v>118</v>
       </c>
       <c r="B56" t="s">
+        <v>109</v>
+      </c>
+      <c r="C56" t="s">
         <v>107</v>
-      </c>
-      <c r="C56" t="s">
-        <v>109</v>
       </c>
       <c r="D56" t="n">
         <v>0.0172567020716671</v>
@@ -13427,10 +13427,10 @@
         <v>119</v>
       </c>
       <c r="B57" t="s">
+        <v>109</v>
+      </c>
+      <c r="C57" t="s">
         <v>107</v>
-      </c>
-      <c r="C57" t="s">
-        <v>109</v>
       </c>
       <c r="D57" t="n">
         <v>0.0146626056368238</v>
@@ -13453,10 +13453,10 @@
         <v>120</v>
       </c>
       <c r="B58" t="s">
+        <v>109</v>
+      </c>
+      <c r="C58" t="s">
         <v>107</v>
-      </c>
-      <c r="C58" t="s">
-        <v>109</v>
       </c>
       <c r="D58" t="n">
         <v>0.0278028384052188</v>
@@ -13479,10 +13479,10 @@
         <v>121</v>
       </c>
       <c r="B59" t="s">
+        <v>109</v>
+      </c>
+      <c r="C59" t="s">
         <v>107</v>
-      </c>
-      <c r="C59" t="s">
-        <v>109</v>
       </c>
       <c r="D59" t="n">
         <v>0.0202724899285924</v>
@@ -13505,10 +13505,10 @@
         <v>122</v>
       </c>
       <c r="B60" t="s">
+        <v>109</v>
+      </c>
+      <c r="C60" t="s">
         <v>107</v>
-      </c>
-      <c r="C60" t="s">
-        <v>109</v>
       </c>
       <c r="D60" t="n">
         <v>0.0128427839283708</v>
@@ -13531,10 +13531,10 @@
         <v>123</v>
       </c>
       <c r="B61" t="s">
+        <v>109</v>
+      </c>
+      <c r="C61" t="s">
         <v>107</v>
-      </c>
-      <c r="C61" t="s">
-        <v>109</v>
       </c>
       <c r="D61" t="n">
         <v>0.0269265356945213</v>
@@ -13557,10 +13557,10 @@
         <v>124</v>
       </c>
       <c r="B62" t="s">
+        <v>109</v>
+      </c>
+      <c r="C62" t="s">
         <v>107</v>
-      </c>
-      <c r="C62" t="s">
-        <v>109</v>
       </c>
       <c r="D62" t="n">
         <v>0.0155818762274729</v>
@@ -13583,10 +13583,10 @@
         <v>125</v>
       </c>
       <c r="B63" t="s">
+        <v>109</v>
+      </c>
+      <c r="C63" t="s">
         <v>107</v>
-      </c>
-      <c r="C63" t="s">
-        <v>109</v>
       </c>
       <c r="D63" t="n">
         <v>0.00909893687017351</v>
@@ -13609,10 +13609,10 @@
         <v>127</v>
       </c>
       <c r="B64" t="s">
+        <v>128</v>
+      </c>
+      <c r="C64" t="s">
         <v>126</v>
-      </c>
-      <c r="C64" t="s">
-        <v>128</v>
       </c>
       <c r="D64" t="n">
         <v>0.00644092120549443</v>
@@ -13635,10 +13635,10 @@
         <v>129</v>
       </c>
       <c r="B65" t="s">
+        <v>128</v>
+      </c>
+      <c r="C65" t="s">
         <v>126</v>
-      </c>
-      <c r="C65" t="s">
-        <v>128</v>
       </c>
       <c r="D65" t="n">
         <v>0.00751931271595517</v>
@@ -13661,10 +13661,10 @@
         <v>130</v>
       </c>
       <c r="B66" t="s">
+        <v>128</v>
+      </c>
+      <c r="C66" t="s">
         <v>126</v>
-      </c>
-      <c r="C66" t="s">
-        <v>128</v>
       </c>
       <c r="D66" t="n">
         <v>0.0132047297414616</v>
@@ -13687,10 +13687,10 @@
         <v>131</v>
       </c>
       <c r="B67" t="s">
+        <v>128</v>
+      </c>
+      <c r="C67" t="s">
         <v>126</v>
-      </c>
-      <c r="C67" t="s">
-        <v>128</v>
       </c>
       <c r="D67" t="n">
         <v>0.0112936958470272</v>
@@ -13713,10 +13713,10 @@
         <v>132</v>
       </c>
       <c r="B68" t="s">
+        <v>128</v>
+      </c>
+      <c r="C68" t="s">
         <v>126</v>
-      </c>
-      <c r="C68" t="s">
-        <v>128</v>
       </c>
       <c r="D68" t="n">
         <v>0.0135488532938768</v>
@@ -13739,10 +13739,10 @@
         <v>133</v>
       </c>
       <c r="B69" t="s">
+        <v>128</v>
+      </c>
+      <c r="C69" t="s">
         <v>126</v>
-      </c>
-      <c r="C69" t="s">
-        <v>128</v>
       </c>
       <c r="D69" t="n">
         <v>0.0559981377062749</v>
@@ -13765,10 +13765,10 @@
         <v>134</v>
       </c>
       <c r="B70" t="s">
+        <v>128</v>
+      </c>
+      <c r="C70" t="s">
         <v>126</v>
-      </c>
-      <c r="C70" t="s">
-        <v>128</v>
       </c>
       <c r="D70" t="n">
         <v>0.0176041950422229</v>
@@ -13791,10 +13791,10 @@
         <v>135</v>
       </c>
       <c r="B71" t="s">
+        <v>128</v>
+      </c>
+      <c r="C71" t="s">
         <v>126</v>
-      </c>
-      <c r="C71" t="s">
-        <v>128</v>
       </c>
       <c r="D71" t="n">
         <v>0.0145412143971741</v>
@@ -13814,13 +13814,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
+        <v>137</v>
+      </c>
+      <c r="B72" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" t="s">
         <v>136</v>
-      </c>
-      <c r="B72" t="s">
-        <v>10</v>
-      </c>
-      <c r="C72" t="s">
-        <v>137</v>
       </c>
       <c r="D72" t="n">
         <v>0.00615037136776268</v>
@@ -13846,7 +13846,7 @@
         <v>10</v>
       </c>
       <c r="C73" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D73" t="n">
         <v>0.0719074627122583</v>
@@ -13872,7 +13872,7 @@
         <v>10</v>
       </c>
       <c r="C74" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D74" t="n">
         <v>0.0293682046278227</v>
@@ -13898,7 +13898,7 @@
         <v>10</v>
       </c>
       <c r="C75" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D75" t="n">
         <v>0.0103442018026738</v>
@@ -13924,7 +13924,7 @@
         <v>10</v>
       </c>
       <c r="C76" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D76" t="n">
         <v>0.0297651981464831</v>
@@ -13950,7 +13950,7 @@
         <v>10</v>
       </c>
       <c r="C77" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D77" t="n">
         <v>0.106482201150319</v>
@@ -13976,7 +13976,7 @@
         <v>10</v>
       </c>
       <c r="C78" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D78" t="n">
         <v>0.0108570886086874</v>
@@ -14002,7 +14002,7 @@
         <v>10</v>
       </c>
       <c r="C79" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D79" t="n">
         <v>0.0301910520784881</v>
@@ -14028,7 +14028,7 @@
         <v>10</v>
       </c>
       <c r="C80" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D80" t="n">
         <v>0.0235615399856994</v>
@@ -14054,7 +14054,7 @@
         <v>10</v>
       </c>
       <c r="C81" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D81" t="n">
         <v>0.0163182049974503</v>
@@ -14074,13 +14074,13 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
+        <v>148</v>
+      </c>
+      <c r="B82" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82" t="s">
         <v>147</v>
-      </c>
-      <c r="B82" t="s">
-        <v>11</v>
-      </c>
-      <c r="C82" t="s">
-        <v>148</v>
       </c>
       <c r="D82" t="n">
         <v>0.0132884388012132</v>
@@ -14106,7 +14106,7 @@
         <v>11</v>
       </c>
       <c r="C83" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D83" t="n">
         <v>0.0080648639323759</v>
@@ -14132,7 +14132,7 @@
         <v>11</v>
       </c>
       <c r="C84" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D84" t="n">
         <v>0.0101275548066597</v>
@@ -14158,7 +14158,7 @@
         <v>11</v>
       </c>
       <c r="C85" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D85" t="n">
         <v>0.0130613217989544</v>
@@ -14184,7 +14184,7 @@
         <v>11</v>
       </c>
       <c r="C86" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D86" t="n">
         <v>0.0187912865002846</v>
@@ -14210,7 +14210,7 @@
         <v>11</v>
       </c>
       <c r="C87" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D87" t="n">
         <v>0.0158989946223989</v>
@@ -14236,7 +14236,7 @@
         <v>11</v>
       </c>
       <c r="C88" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D88" t="n">
         <v>0.0128488028633978</v>
@@ -14262,7 +14262,7 @@
         <v>11</v>
       </c>
       <c r="C89" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D89" t="n">
         <v>0.0491340980259857</v>
@@ -14285,10 +14285,10 @@
         <v>157</v>
       </c>
       <c r="B90" t="s">
+        <v>158</v>
+      </c>
+      <c r="C90" t="s">
         <v>156</v>
-      </c>
-      <c r="C90" t="s">
-        <v>158</v>
       </c>
       <c r="D90" t="n">
         <v>0.0969842953790501</v>
@@ -14311,10 +14311,10 @@
         <v>159</v>
       </c>
       <c r="B91" t="s">
+        <v>158</v>
+      </c>
+      <c r="C91" t="s">
         <v>156</v>
-      </c>
-      <c r="C91" t="s">
-        <v>158</v>
       </c>
       <c r="D91" t="n">
         <v>0.0335619942935937</v>
@@ -14337,10 +14337,10 @@
         <v>160</v>
       </c>
       <c r="B92" t="s">
+        <v>158</v>
+      </c>
+      <c r="C92" t="s">
         <v>156</v>
-      </c>
-      <c r="C92" t="s">
-        <v>158</v>
       </c>
       <c r="D92" t="n">
         <v>0.0243415561731529</v>
@@ -14363,10 +14363,10 @@
         <v>161</v>
       </c>
       <c r="B93" t="s">
+        <v>158</v>
+      </c>
+      <c r="C93" t="s">
         <v>156</v>
-      </c>
-      <c r="C93" t="s">
-        <v>158</v>
       </c>
       <c r="D93" t="n">
         <v>0.0150212360232296</v>
@@ -14389,10 +14389,10 @@
         <v>162</v>
       </c>
       <c r="B94" t="s">
+        <v>158</v>
+      </c>
+      <c r="C94" t="s">
         <v>156</v>
-      </c>
-      <c r="C94" t="s">
-        <v>158</v>
       </c>
       <c r="D94" t="n">
         <v>0.0168353336698119</v>
@@ -14415,10 +14415,10 @@
         <v>163</v>
       </c>
       <c r="B95" t="s">
+        <v>158</v>
+      </c>
+      <c r="C95" t="s">
         <v>156</v>
-      </c>
-      <c r="C95" t="s">
-        <v>158</v>
       </c>
       <c r="D95" t="n">
         <v>0.0117642994109213</v>
@@ -14441,10 +14441,10 @@
         <v>164</v>
       </c>
       <c r="B96" t="s">
+        <v>158</v>
+      </c>
+      <c r="C96" t="s">
         <v>156</v>
-      </c>
-      <c r="C96" t="s">
-        <v>158</v>
       </c>
       <c r="D96" t="n">
         <v>0.02573864319967</v>
@@ -14467,10 +14467,10 @@
         <v>166</v>
       </c>
       <c r="B97" t="s">
+        <v>167</v>
+      </c>
+      <c r="C97" t="s">
         <v>165</v>
-      </c>
-      <c r="C97" t="s">
-        <v>167</v>
       </c>
       <c r="D97" t="n">
         <v>0.0188314156387132</v>
@@ -14493,10 +14493,10 @@
         <v>168</v>
       </c>
       <c r="B98" t="s">
+        <v>167</v>
+      </c>
+      <c r="C98" t="s">
         <v>165</v>
-      </c>
-      <c r="C98" t="s">
-        <v>167</v>
       </c>
       <c r="D98" t="n">
         <v>0.0274429385054154</v>
@@ -14519,10 +14519,10 @@
         <v>169</v>
       </c>
       <c r="B99" t="s">
+        <v>167</v>
+      </c>
+      <c r="C99" t="s">
         <v>165</v>
-      </c>
-      <c r="C99" t="s">
-        <v>167</v>
       </c>
       <c r="D99" t="n">
         <v>0.0344777033261756</v>
@@ -14545,10 +14545,10 @@
         <v>170</v>
       </c>
       <c r="B100" t="s">
+        <v>167</v>
+      </c>
+      <c r="C100" t="s">
         <v>165</v>
-      </c>
-      <c r="C100" t="s">
-        <v>167</v>
       </c>
       <c r="D100" t="n">
         <v>0.0122764670767474</v>
@@ -14571,10 +14571,10 @@
         <v>171</v>
       </c>
       <c r="B101" t="s">
+        <v>167</v>
+      </c>
+      <c r="C101" t="s">
         <v>165</v>
-      </c>
-      <c r="C101" t="s">
-        <v>167</v>
       </c>
       <c r="D101" t="n">
         <v>0.0196887516327996</v>
@@ -14597,10 +14597,10 @@
         <v>172</v>
       </c>
       <c r="B102" t="s">
+        <v>167</v>
+      </c>
+      <c r="C102" t="s">
         <v>165</v>
-      </c>
-      <c r="C102" t="s">
-        <v>167</v>
       </c>
       <c r="D102" t="n">
         <v>0.023931431734445</v>
@@ -14623,10 +14623,10 @@
         <v>173</v>
       </c>
       <c r="B103" t="s">
+        <v>167</v>
+      </c>
+      <c r="C103" t="s">
         <v>165</v>
-      </c>
-      <c r="C103" t="s">
-        <v>167</v>
       </c>
       <c r="D103" t="n">
         <v>0.0347959729921083</v>
@@ -14646,13 +14646,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
+        <v>175</v>
+      </c>
+      <c r="B104" t="s">
+        <v>29</v>
+      </c>
+      <c r="C104" t="s">
         <v>174</v>
-      </c>
-      <c r="B104" t="s">
-        <v>29</v>
-      </c>
-      <c r="C104" t="s">
-        <v>175</v>
       </c>
       <c r="D104" t="n">
         <v>0.0361782672287705</v>
@@ -14678,7 +14678,7 @@
         <v>29</v>
       </c>
       <c r="C105" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D105" t="n">
         <v>0.0363357436502943</v>
@@ -14704,7 +14704,7 @@
         <v>29</v>
       </c>
       <c r="C106" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D106" t="n">
         <v>0.0351941432514993</v>
@@ -14730,7 +14730,7 @@
         <v>29</v>
       </c>
       <c r="C107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D107" t="n">
         <v>0.0611002167406338</v>
@@ -14756,7 +14756,7 @@
         <v>29</v>
       </c>
       <c r="C108" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D108" t="n">
         <v>0.0134634079197529</v>
@@ -14790,10 +14790,10 @@
         <v>48</v>
       </c>
       <c r="B1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" t="s">
         <v>47</v>
-      </c>
-      <c r="C1" t="s">
-        <v>49</v>
       </c>
       <c r="D1" t="s">
         <v>185</v>
@@ -14816,10 +14816,10 @@
         <v>190</v>
       </c>
       <c r="B2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" t="s">
         <v>52</v>
-      </c>
-      <c r="C2" t="s">
-        <v>54</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -14842,10 +14842,10 @@
         <v>191</v>
       </c>
       <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" t="s">
         <v>52</v>
-      </c>
-      <c r="C3" t="s">
-        <v>54</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -14868,10 +14868,10 @@
         <v>192</v>
       </c>
       <c r="B4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" t="s">
         <v>52</v>
-      </c>
-      <c r="C4" t="s">
-        <v>54</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -14894,10 +14894,10 @@
         <v>193</v>
       </c>
       <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" t="s">
         <v>52</v>
-      </c>
-      <c r="C5" t="s">
-        <v>54</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -14920,10 +14920,10 @@
         <v>194</v>
       </c>
       <c r="B6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" t="s">
         <v>52</v>
-      </c>
-      <c r="C6" t="s">
-        <v>54</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -14946,10 +14946,10 @@
         <v>195</v>
       </c>
       <c r="B7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" t="s">
         <v>52</v>
-      </c>
-      <c r="C7" t="s">
-        <v>54</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -14972,10 +14972,10 @@
         <v>196</v>
       </c>
       <c r="B8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" t="s">
         <v>52</v>
-      </c>
-      <c r="C8" t="s">
-        <v>54</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -14998,10 +14998,10 @@
         <v>197</v>
       </c>
       <c r="B9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" t="s">
         <v>52</v>
-      </c>
-      <c r="C9" t="s">
-        <v>54</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -15024,10 +15024,10 @@
         <v>198</v>
       </c>
       <c r="B10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" t="s">
         <v>58</v>
-      </c>
-      <c r="C10" t="s">
-        <v>60</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -15050,10 +15050,10 @@
         <v>199</v>
       </c>
       <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
         <v>58</v>
-      </c>
-      <c r="C11" t="s">
-        <v>60</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -15076,10 +15076,10 @@
         <v>200</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -15102,10 +15102,10 @@
         <v>201</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -15128,10 +15128,10 @@
         <v>202</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -15154,10 +15154,10 @@
         <v>203</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -15180,10 +15180,10 @@
         <v>204</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -15206,10 +15206,10 @@
         <v>205</v>
       </c>
       <c r="B17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -15232,10 +15232,10 @@
         <v>206</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -15258,10 +15258,10 @@
         <v>207</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -15284,10 +15284,10 @@
         <v>208</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -15310,10 +15310,10 @@
         <v>209</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -15336,10 +15336,10 @@
         <v>210</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -15362,10 +15362,10 @@
         <v>211</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -15388,10 +15388,10 @@
         <v>212</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>213</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -15440,10 +15440,10 @@
         <v>214</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -15466,10 +15466,10 @@
         <v>215</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -15492,10 +15492,10 @@
         <v>216</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -15518,10 +15518,10 @@
         <v>217</v>
       </c>
       <c r="B29" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" t="s">
         <v>81</v>
-      </c>
-      <c r="C29" t="s">
-        <v>83</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -15544,10 +15544,10 @@
         <v>218</v>
       </c>
       <c r="B30" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" t="s">
         <v>81</v>
-      </c>
-      <c r="C30" t="s">
-        <v>83</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -15570,10 +15570,10 @@
         <v>219</v>
       </c>
       <c r="B31" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" t="s">
         <v>81</v>
-      </c>
-      <c r="C31" t="s">
-        <v>83</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -15596,10 +15596,10 @@
         <v>220</v>
       </c>
       <c r="B32" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" t="s">
         <v>81</v>
-      </c>
-      <c r="C32" t="s">
-        <v>83</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -15622,10 +15622,10 @@
         <v>221</v>
       </c>
       <c r="B33" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" t="s">
         <v>81</v>
-      </c>
-      <c r="C33" t="s">
-        <v>83</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -15648,10 +15648,10 @@
         <v>222</v>
       </c>
       <c r="B34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" t="s">
         <v>81</v>
-      </c>
-      <c r="C34" t="s">
-        <v>83</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -15674,10 +15674,10 @@
         <v>223</v>
       </c>
       <c r="B35" t="s">
+        <v>83</v>
+      </c>
+      <c r="C35" t="s">
         <v>81</v>
-      </c>
-      <c r="C35" t="s">
-        <v>83</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -15700,10 +15700,10 @@
         <v>224</v>
       </c>
       <c r="B36" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" t="s">
         <v>81</v>
-      </c>
-      <c r="C36" t="s">
-        <v>83</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -15726,10 +15726,10 @@
         <v>225</v>
       </c>
       <c r="B37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" t="s">
         <v>81</v>
-      </c>
-      <c r="C37" t="s">
-        <v>83</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -15752,10 +15752,10 @@
         <v>226</v>
       </c>
       <c r="B38" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" t="s">
         <v>81</v>
-      </c>
-      <c r="C38" t="s">
-        <v>83</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -15778,10 +15778,10 @@
         <v>227</v>
       </c>
       <c r="B39" t="s">
+        <v>83</v>
+      </c>
+      <c r="C39" t="s">
         <v>81</v>
-      </c>
-      <c r="C39" t="s">
-        <v>83</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -15804,10 +15804,10 @@
         <v>228</v>
       </c>
       <c r="B40" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" t="s">
         <v>81</v>
-      </c>
-      <c r="C40" t="s">
-        <v>83</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -15830,10 +15830,10 @@
         <v>229</v>
       </c>
       <c r="B41" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41" t="s">
         <v>81</v>
-      </c>
-      <c r="C41" t="s">
-        <v>83</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -15856,10 +15856,10 @@
         <v>230</v>
       </c>
       <c r="B42" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" t="s">
         <v>81</v>
-      </c>
-      <c r="C42" t="s">
-        <v>83</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -15882,10 +15882,10 @@
         <v>231</v>
       </c>
       <c r="B43" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" t="s">
         <v>81</v>
-      </c>
-      <c r="C43" t="s">
-        <v>83</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -15908,10 +15908,10 @@
         <v>232</v>
       </c>
       <c r="B44" t="s">
+        <v>83</v>
+      </c>
+      <c r="C44" t="s">
         <v>81</v>
-      </c>
-      <c r="C44" t="s">
-        <v>83</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -15934,10 +15934,10 @@
         <v>233</v>
       </c>
       <c r="B45" t="s">
+        <v>83</v>
+      </c>
+      <c r="C45" t="s">
         <v>81</v>
-      </c>
-      <c r="C45" t="s">
-        <v>83</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -15960,10 +15960,10 @@
         <v>234</v>
       </c>
       <c r="B46" t="s">
+        <v>98</v>
+      </c>
+      <c r="C46" t="s">
         <v>96</v>
-      </c>
-      <c r="C46" t="s">
-        <v>98</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -15986,10 +15986,10 @@
         <v>235</v>
       </c>
       <c r="B47" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" t="s">
         <v>96</v>
-      </c>
-      <c r="C47" t="s">
-        <v>98</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -16012,10 +16012,10 @@
         <v>236</v>
       </c>
       <c r="B48" t="s">
+        <v>98</v>
+      </c>
+      <c r="C48" t="s">
         <v>96</v>
-      </c>
-      <c r="C48" t="s">
-        <v>98</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -16038,10 +16038,10 @@
         <v>237</v>
       </c>
       <c r="B49" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49" t="s">
         <v>96</v>
-      </c>
-      <c r="C49" t="s">
-        <v>98</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -16064,10 +16064,10 @@
         <v>238</v>
       </c>
       <c r="B50" t="s">
+        <v>98</v>
+      </c>
+      <c r="C50" t="s">
         <v>96</v>
-      </c>
-      <c r="C50" t="s">
-        <v>98</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -16090,10 +16090,10 @@
         <v>239</v>
       </c>
       <c r="B51" t="s">
+        <v>98</v>
+      </c>
+      <c r="C51" t="s">
         <v>96</v>
-      </c>
-      <c r="C51" t="s">
-        <v>98</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -16116,10 +16116,10 @@
         <v>240</v>
       </c>
       <c r="B52" t="s">
+        <v>98</v>
+      </c>
+      <c r="C52" t="s">
         <v>96</v>
-      </c>
-      <c r="C52" t="s">
-        <v>98</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -16142,10 +16142,10 @@
         <v>241</v>
       </c>
       <c r="B53" t="s">
+        <v>98</v>
+      </c>
+      <c r="C53" t="s">
         <v>96</v>
-      </c>
-      <c r="C53" t="s">
-        <v>98</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -16168,10 +16168,10 @@
         <v>242</v>
       </c>
       <c r="B54" t="s">
+        <v>98</v>
+      </c>
+      <c r="C54" t="s">
         <v>96</v>
-      </c>
-      <c r="C54" t="s">
-        <v>98</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
@@ -16194,10 +16194,10 @@
         <v>243</v>
       </c>
       <c r="B55" t="s">
+        <v>98</v>
+      </c>
+      <c r="C55" t="s">
         <v>96</v>
-      </c>
-      <c r="C55" t="s">
-        <v>98</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -16220,10 +16220,10 @@
         <v>244</v>
       </c>
       <c r="B56" t="s">
+        <v>98</v>
+      </c>
+      <c r="C56" t="s">
         <v>96</v>
-      </c>
-      <c r="C56" t="s">
-        <v>98</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -16246,10 +16246,10 @@
         <v>245</v>
       </c>
       <c r="B57" t="s">
+        <v>109</v>
+      </c>
+      <c r="C57" t="s">
         <v>107</v>
-      </c>
-      <c r="C57" t="s">
-        <v>109</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -16272,10 +16272,10 @@
         <v>246</v>
       </c>
       <c r="B58" t="s">
+        <v>109</v>
+      </c>
+      <c r="C58" t="s">
         <v>107</v>
-      </c>
-      <c r="C58" t="s">
-        <v>109</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -16298,10 +16298,10 @@
         <v>247</v>
       </c>
       <c r="B59" t="s">
+        <v>109</v>
+      </c>
+      <c r="C59" t="s">
         <v>107</v>
-      </c>
-      <c r="C59" t="s">
-        <v>109</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -16324,10 +16324,10 @@
         <v>248</v>
       </c>
       <c r="B60" t="s">
+        <v>109</v>
+      </c>
+      <c r="C60" t="s">
         <v>107</v>
-      </c>
-      <c r="C60" t="s">
-        <v>109</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -16350,10 +16350,10 @@
         <v>249</v>
       </c>
       <c r="B61" t="s">
+        <v>109</v>
+      </c>
+      <c r="C61" t="s">
         <v>107</v>
-      </c>
-      <c r="C61" t="s">
-        <v>109</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -16376,10 +16376,10 @@
         <v>250</v>
       </c>
       <c r="B62" t="s">
+        <v>109</v>
+      </c>
+      <c r="C62" t="s">
         <v>107</v>
-      </c>
-      <c r="C62" t="s">
-        <v>109</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -16402,10 +16402,10 @@
         <v>251</v>
       </c>
       <c r="B63" t="s">
+        <v>109</v>
+      </c>
+      <c r="C63" t="s">
         <v>107</v>
-      </c>
-      <c r="C63" t="s">
-        <v>109</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -16428,10 +16428,10 @@
         <v>252</v>
       </c>
       <c r="B64" t="s">
+        <v>109</v>
+      </c>
+      <c r="C64" t="s">
         <v>107</v>
-      </c>
-      <c r="C64" t="s">
-        <v>109</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -16454,10 +16454,10 @@
         <v>253</v>
       </c>
       <c r="B65" t="s">
+        <v>109</v>
+      </c>
+      <c r="C65" t="s">
         <v>107</v>
-      </c>
-      <c r="C65" t="s">
-        <v>109</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -16480,10 +16480,10 @@
         <v>254</v>
       </c>
       <c r="B66" t="s">
+        <v>109</v>
+      </c>
+      <c r="C66" t="s">
         <v>107</v>
-      </c>
-      <c r="C66" t="s">
-        <v>109</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -16506,10 +16506,10 @@
         <v>255</v>
       </c>
       <c r="B67" t="s">
+        <v>109</v>
+      </c>
+      <c r="C67" t="s">
         <v>107</v>
-      </c>
-      <c r="C67" t="s">
-        <v>109</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -16532,10 +16532,10 @@
         <v>256</v>
       </c>
       <c r="B68" t="s">
+        <v>109</v>
+      </c>
+      <c r="C68" t="s">
         <v>107</v>
-      </c>
-      <c r="C68" t="s">
-        <v>109</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -16558,10 +16558,10 @@
         <v>257</v>
       </c>
       <c r="B69" t="s">
+        <v>109</v>
+      </c>
+      <c r="C69" t="s">
         <v>107</v>
-      </c>
-      <c r="C69" t="s">
-        <v>109</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
@@ -16584,10 +16584,10 @@
         <v>258</v>
       </c>
       <c r="B70" t="s">
+        <v>109</v>
+      </c>
+      <c r="C70" t="s">
         <v>107</v>
-      </c>
-      <c r="C70" t="s">
-        <v>109</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
@@ -16610,10 +16610,10 @@
         <v>259</v>
       </c>
       <c r="B71" t="s">
+        <v>109</v>
+      </c>
+      <c r="C71" t="s">
         <v>107</v>
-      </c>
-      <c r="C71" t="s">
-        <v>109</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -16636,10 +16636,10 @@
         <v>260</v>
       </c>
       <c r="B72" t="s">
+        <v>109</v>
+      </c>
+      <c r="C72" t="s">
         <v>107</v>
-      </c>
-      <c r="C72" t="s">
-        <v>109</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -16662,10 +16662,10 @@
         <v>261</v>
       </c>
       <c r="B73" t="s">
+        <v>109</v>
+      </c>
+      <c r="C73" t="s">
         <v>107</v>
-      </c>
-      <c r="C73" t="s">
-        <v>109</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
@@ -16688,10 +16688,10 @@
         <v>262</v>
       </c>
       <c r="B74" t="s">
+        <v>109</v>
+      </c>
+      <c r="C74" t="s">
         <v>107</v>
-      </c>
-      <c r="C74" t="s">
-        <v>109</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
@@ -16714,10 +16714,10 @@
         <v>263</v>
       </c>
       <c r="B75" t="s">
+        <v>109</v>
+      </c>
+      <c r="C75" t="s">
         <v>107</v>
-      </c>
-      <c r="C75" t="s">
-        <v>109</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -16740,10 +16740,10 @@
         <v>264</v>
       </c>
       <c r="B76" t="s">
+        <v>109</v>
+      </c>
+      <c r="C76" t="s">
         <v>107</v>
-      </c>
-      <c r="C76" t="s">
-        <v>109</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -16766,10 +16766,10 @@
         <v>265</v>
       </c>
       <c r="B77" t="s">
+        <v>128</v>
+      </c>
+      <c r="C77" t="s">
         <v>126</v>
-      </c>
-      <c r="C77" t="s">
-        <v>128</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
@@ -16792,10 +16792,10 @@
         <v>266</v>
       </c>
       <c r="B78" t="s">
+        <v>128</v>
+      </c>
+      <c r="C78" t="s">
         <v>126</v>
-      </c>
-      <c r="C78" t="s">
-        <v>128</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -16818,10 +16818,10 @@
         <v>267</v>
       </c>
       <c r="B79" t="s">
+        <v>128</v>
+      </c>
+      <c r="C79" t="s">
         <v>126</v>
-      </c>
-      <c r="C79" t="s">
-        <v>128</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -16844,10 +16844,10 @@
         <v>268</v>
       </c>
       <c r="B80" t="s">
+        <v>128</v>
+      </c>
+      <c r="C80" t="s">
         <v>126</v>
-      </c>
-      <c r="C80" t="s">
-        <v>128</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
@@ -16870,10 +16870,10 @@
         <v>269</v>
       </c>
       <c r="B81" t="s">
+        <v>128</v>
+      </c>
+      <c r="C81" t="s">
         <v>126</v>
-      </c>
-      <c r="C81" t="s">
-        <v>128</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -16896,10 +16896,10 @@
         <v>270</v>
       </c>
       <c r="B82" t="s">
+        <v>128</v>
+      </c>
+      <c r="C82" t="s">
         <v>126</v>
-      </c>
-      <c r="C82" t="s">
-        <v>128</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
@@ -16922,10 +16922,10 @@
         <v>271</v>
       </c>
       <c r="B83" t="s">
+        <v>128</v>
+      </c>
+      <c r="C83" t="s">
         <v>126</v>
-      </c>
-      <c r="C83" t="s">
-        <v>128</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -16948,10 +16948,10 @@
         <v>272</v>
       </c>
       <c r="B84" t="s">
+        <v>128</v>
+      </c>
+      <c r="C84" t="s">
         <v>126</v>
-      </c>
-      <c r="C84" t="s">
-        <v>128</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -16974,10 +16974,10 @@
         <v>273</v>
       </c>
       <c r="B85" t="s">
+        <v>128</v>
+      </c>
+      <c r="C85" t="s">
         <v>126</v>
-      </c>
-      <c r="C85" t="s">
-        <v>128</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
@@ -17003,7 +17003,7 @@
         <v>10</v>
       </c>
       <c r="C86" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -17029,7 +17029,7 @@
         <v>10</v>
       </c>
       <c r="C87" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
@@ -17055,7 +17055,7 @@
         <v>10</v>
       </c>
       <c r="C88" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D88" t="n">
         <v>0</v>
@@ -17081,7 +17081,7 @@
         <v>10</v>
       </c>
       <c r="C89" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
@@ -17107,7 +17107,7 @@
         <v>10</v>
       </c>
       <c r="C90" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
@@ -17133,7 +17133,7 @@
         <v>10</v>
       </c>
       <c r="C91" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
@@ -17159,7 +17159,7 @@
         <v>10</v>
       </c>
       <c r="C92" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
@@ -17185,7 +17185,7 @@
         <v>10</v>
       </c>
       <c r="C93" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
@@ -17211,7 +17211,7 @@
         <v>10</v>
       </c>
       <c r="C94" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
@@ -17237,7 +17237,7 @@
         <v>11</v>
       </c>
       <c r="C95" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
@@ -17263,7 +17263,7 @@
         <v>11</v>
       </c>
       <c r="C96" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D96" t="n">
         <v>0</v>
@@ -17289,7 +17289,7 @@
         <v>11</v>
       </c>
       <c r="C97" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
@@ -17315,7 +17315,7 @@
         <v>11</v>
       </c>
       <c r="C98" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
@@ -17341,7 +17341,7 @@
         <v>11</v>
       </c>
       <c r="C99" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
@@ -17367,7 +17367,7 @@
         <v>11</v>
       </c>
       <c r="C100" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -17393,7 +17393,7 @@
         <v>11</v>
       </c>
       <c r="C101" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
@@ -17419,7 +17419,7 @@
         <v>11</v>
       </c>
       <c r="C102" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
@@ -17442,10 +17442,10 @@
         <v>274</v>
       </c>
       <c r="B103" t="s">
+        <v>158</v>
+      </c>
+      <c r="C103" t="s">
         <v>156</v>
-      </c>
-      <c r="C103" t="s">
-        <v>158</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
@@ -17468,10 +17468,10 @@
         <v>275</v>
       </c>
       <c r="B104" t="s">
+        <v>158</v>
+      </c>
+      <c r="C104" t="s">
         <v>156</v>
-      </c>
-      <c r="C104" t="s">
-        <v>158</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
@@ -17494,10 +17494,10 @@
         <v>276</v>
       </c>
       <c r="B105" t="s">
+        <v>158</v>
+      </c>
+      <c r="C105" t="s">
         <v>156</v>
-      </c>
-      <c r="C105" t="s">
-        <v>158</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
@@ -17520,10 +17520,10 @@
         <v>277</v>
       </c>
       <c r="B106" t="s">
+        <v>158</v>
+      </c>
+      <c r="C106" t="s">
         <v>156</v>
-      </c>
-      <c r="C106" t="s">
-        <v>158</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
@@ -17546,10 +17546,10 @@
         <v>278</v>
       </c>
       <c r="B107" t="s">
+        <v>158</v>
+      </c>
+      <c r="C107" t="s">
         <v>156</v>
-      </c>
-      <c r="C107" t="s">
-        <v>158</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
@@ -17572,10 +17572,10 @@
         <v>279</v>
       </c>
       <c r="B108" t="s">
+        <v>158</v>
+      </c>
+      <c r="C108" t="s">
         <v>156</v>
-      </c>
-      <c r="C108" t="s">
-        <v>158</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -17598,10 +17598,10 @@
         <v>280</v>
       </c>
       <c r="B109" t="s">
+        <v>158</v>
+      </c>
+      <c r="C109" t="s">
         <v>156</v>
-      </c>
-      <c r="C109" t="s">
-        <v>158</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
@@ -17624,10 +17624,10 @@
         <v>281</v>
       </c>
       <c r="B110" t="s">
+        <v>158</v>
+      </c>
+      <c r="C110" t="s">
         <v>156</v>
-      </c>
-      <c r="C110" t="s">
-        <v>158</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -17650,10 +17650,10 @@
         <v>282</v>
       </c>
       <c r="B111" t="s">
+        <v>167</v>
+      </c>
+      <c r="C111" t="s">
         <v>165</v>
-      </c>
-      <c r="C111" t="s">
-        <v>167</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -17676,10 +17676,10 @@
         <v>283</v>
       </c>
       <c r="B112" t="s">
+        <v>167</v>
+      </c>
+      <c r="C112" t="s">
         <v>165</v>
-      </c>
-      <c r="C112" t="s">
-        <v>167</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
@@ -17702,10 +17702,10 @@
         <v>284</v>
       </c>
       <c r="B113" t="s">
+        <v>167</v>
+      </c>
+      <c r="C113" t="s">
         <v>165</v>
-      </c>
-      <c r="C113" t="s">
-        <v>167</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -17728,10 +17728,10 @@
         <v>285</v>
       </c>
       <c r="B114" t="s">
+        <v>167</v>
+      </c>
+      <c r="C114" t="s">
         <v>165</v>
-      </c>
-      <c r="C114" t="s">
-        <v>167</v>
       </c>
       <c r="D114" t="n">
         <v>0</v>
@@ -17754,10 +17754,10 @@
         <v>286</v>
       </c>
       <c r="B115" t="s">
+        <v>167</v>
+      </c>
+      <c r="C115" t="s">
         <v>165</v>
-      </c>
-      <c r="C115" t="s">
-        <v>167</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
@@ -17780,10 +17780,10 @@
         <v>287</v>
       </c>
       <c r="B116" t="s">
+        <v>167</v>
+      </c>
+      <c r="C116" t="s">
         <v>165</v>
-      </c>
-      <c r="C116" t="s">
-        <v>167</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -17806,10 +17806,10 @@
         <v>288</v>
       </c>
       <c r="B117" t="s">
+        <v>167</v>
+      </c>
+      <c r="C117" t="s">
         <v>165</v>
-      </c>
-      <c r="C117" t="s">
-        <v>167</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -17832,10 +17832,10 @@
         <v>289</v>
       </c>
       <c r="B118" t="s">
+        <v>167</v>
+      </c>
+      <c r="C118" t="s">
         <v>165</v>
-      </c>
-      <c r="C118" t="s">
-        <v>167</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -17858,10 +17858,10 @@
         <v>290</v>
       </c>
       <c r="B119" t="s">
+        <v>167</v>
+      </c>
+      <c r="C119" t="s">
         <v>165</v>
-      </c>
-      <c r="C119" t="s">
-        <v>167</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
@@ -17884,10 +17884,10 @@
         <v>291</v>
       </c>
       <c r="B120" t="s">
+        <v>167</v>
+      </c>
+      <c r="C120" t="s">
         <v>165</v>
-      </c>
-      <c r="C120" t="s">
-        <v>167</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
@@ -17910,10 +17910,10 @@
         <v>292</v>
       </c>
       <c r="B121" t="s">
+        <v>167</v>
+      </c>
+      <c r="C121" t="s">
         <v>165</v>
-      </c>
-      <c r="C121" t="s">
-        <v>167</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
@@ -17936,10 +17936,10 @@
         <v>293</v>
       </c>
       <c r="B122" t="s">
+        <v>167</v>
+      </c>
+      <c r="C122" t="s">
         <v>165</v>
-      </c>
-      <c r="C122" t="s">
-        <v>167</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -17965,7 +17965,7 @@
         <v>29</v>
       </c>
       <c r="C123" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D123" t="n">
         <v>0</v>
@@ -17991,7 +17991,7 @@
         <v>29</v>
       </c>
       <c r="C124" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -18017,7 +18017,7 @@
         <v>29</v>
       </c>
       <c r="C125" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
@@ -18043,7 +18043,7 @@
         <v>29</v>
       </c>
       <c r="C126" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -18069,7 +18069,7 @@
         <v>29</v>
       </c>
       <c r="C127" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -18095,7 +18095,7 @@
         <v>29</v>
       </c>
       <c r="C128" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -18121,7 +18121,7 @@
         <v>29</v>
       </c>
       <c r="C129" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -18147,7 +18147,7 @@
         <v>29</v>
       </c>
       <c r="C130" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
@@ -18173,7 +18173,7 @@
         <v>29</v>
       </c>
       <c r="C131" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
@@ -18199,7 +18199,7 @@
         <v>29</v>
       </c>
       <c r="C132" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -18225,7 +18225,7 @@
         <v>29</v>
       </c>
       <c r="C133" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -18251,7 +18251,7 @@
         <v>29</v>
       </c>
       <c r="C134" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
@@ -18277,7 +18277,7 @@
         <v>29</v>
       </c>
       <c r="C135" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
@@ -18303,7 +18303,7 @@
         <v>29</v>
       </c>
       <c r="C136" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
@@ -18329,7 +18329,7 @@
         <v>29</v>
       </c>
       <c r="C137" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
@@ -18355,7 +18355,7 @@
         <v>29</v>
       </c>
       <c r="C138" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
@@ -18381,7 +18381,7 @@
         <v>29</v>
       </c>
       <c r="C139" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
@@ -18438,10 +18438,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D2" t="n">
         <v>0.0216016485468628</v>
@@ -18461,7 +18461,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C3" t="s">
         <v>138</v>
@@ -18484,7 +18484,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C4" t="s">
         <v>139</v>
@@ -18507,7 +18507,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C5" t="s">
         <v>140</v>
@@ -18530,7 +18530,7 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="s">
         <v>141</v>
@@ -18553,7 +18553,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C7" t="s">
         <v>142</v>
@@ -18576,7 +18576,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C8" t="s">
         <v>143</v>
@@ -18599,7 +18599,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C9" t="s">
         <v>144</v>
@@ -18622,7 +18622,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C10" t="s">
         <v>145</v>
@@ -18645,7 +18645,7 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C11" t="s">
         <v>146</v>
@@ -18671,7 +18671,7 @@
         <v>149</v>
       </c>
       <c r="C12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D12" t="n">
         <v>0.0284685001317986</v>
@@ -18901,7 +18901,7 @@
         <v>150</v>
       </c>
       <c r="C22" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D22" t="n">
         <v>0.0281894081764688</v>
@@ -19131,7 +19131,7 @@
         <v>151</v>
       </c>
       <c r="C32" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D32" t="n">
         <v>0.0262152670815107</v>
@@ -19361,7 +19361,7 @@
         <v>152</v>
       </c>
       <c r="C42" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D42" t="n">
         <v>0.013196093956189</v>
@@ -19591,7 +19591,7 @@
         <v>153</v>
       </c>
       <c r="C52" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D52" t="n">
         <v>0.0143022806339389</v>
@@ -19821,7 +19821,7 @@
         <v>154</v>
       </c>
       <c r="C62" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D62" t="n">
         <v>0.0228695623966004</v>
@@ -20051,7 +20051,7 @@
         <v>155</v>
       </c>
       <c r="C72" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D72" t="n">
         <v>0.0223991867163673</v>
@@ -20278,10 +20278,10 @@
         <v>27</v>
       </c>
       <c r="B82" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C82" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D82" t="n">
         <v>0.00853725120365315</v>
@@ -20301,7 +20301,7 @@
         <v>27</v>
       </c>
       <c r="B83" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C83" t="s">
         <v>138</v>
@@ -20324,7 +20324,7 @@
         <v>27</v>
       </c>
       <c r="B84" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C84" t="s">
         <v>139</v>
@@ -20347,7 +20347,7 @@
         <v>27</v>
       </c>
       <c r="B85" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C85" t="s">
         <v>140</v>
@@ -20370,7 +20370,7 @@
         <v>27</v>
       </c>
       <c r="B86" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C86" t="s">
         <v>141</v>
@@ -20393,7 +20393,7 @@
         <v>27</v>
       </c>
       <c r="B87" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C87" t="s">
         <v>142</v>
@@ -20416,7 +20416,7 @@
         <v>27</v>
       </c>
       <c r="B88" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C88" t="s">
         <v>143</v>
@@ -20439,7 +20439,7 @@
         <v>27</v>
       </c>
       <c r="B89" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C89" t="s">
         <v>144</v>
@@ -20462,7 +20462,7 @@
         <v>27</v>
       </c>
       <c r="B90" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C90" t="s">
         <v>145</v>
@@ -20485,7 +20485,7 @@
         <v>27</v>
       </c>
       <c r="B91" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C91" t="s">
         <v>146</v>
@@ -20511,7 +20511,7 @@
         <v>176</v>
       </c>
       <c r="C92" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D92" t="n">
         <v>0.0111851383552984</v>
@@ -20741,7 +20741,7 @@
         <v>177</v>
       </c>
       <c r="C102" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D102" t="n">
         <v>0.0134915096534078</v>
@@ -20971,7 +20971,7 @@
         <v>178</v>
       </c>
       <c r="C112" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D112" t="n">
         <v>0.0155352480417755</v>
@@ -21201,7 +21201,7 @@
         <v>179</v>
       </c>
       <c r="C122" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D122" t="n">
         <v>0.016549801837899</v>
@@ -21428,10 +21428,10 @@
         <v>46</v>
       </c>
       <c r="B132" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C132" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D132" t="n">
         <v>0.0105037354833937</v>
@@ -21451,7 +21451,7 @@
         <v>46</v>
       </c>
       <c r="B133" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C133" t="s">
         <v>149</v>
@@ -21474,7 +21474,7 @@
         <v>46</v>
       </c>
       <c r="B134" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C134" t="s">
         <v>150</v>
@@ -21497,7 +21497,7 @@
         <v>46</v>
       </c>
       <c r="B135" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C135" t="s">
         <v>151</v>
@@ -21520,7 +21520,7 @@
         <v>46</v>
       </c>
       <c r="B136" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C136" t="s">
         <v>152</v>
@@ -21543,7 +21543,7 @@
         <v>46</v>
       </c>
       <c r="B137" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C137" t="s">
         <v>153</v>
@@ -21566,7 +21566,7 @@
         <v>46</v>
       </c>
       <c r="B138" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C138" t="s">
         <v>154</v>
@@ -21589,7 +21589,7 @@
         <v>46</v>
       </c>
       <c r="B139" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C139" t="s">
         <v>155</v>
@@ -21615,7 +21615,7 @@
         <v>176</v>
       </c>
       <c r="C140" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D140" t="n">
         <v>0.0132616487455197</v>
@@ -21799,7 +21799,7 @@
         <v>177</v>
       </c>
       <c r="C148" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D148" t="n">
         <v>0.0153711907638609</v>
@@ -21983,7 +21983,7 @@
         <v>178</v>
       </c>
       <c r="C156" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D156" t="n">
         <v>0.019374159638186</v>
@@ -22167,7 +22167,7 @@
         <v>179</v>
       </c>
       <c r="C164" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D164" t="n">
         <v>0.0193071424207246</v>
